--- a/sample_data/제품마스터.xlsx
+++ b/sample_data/제품마스터.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,15 +430,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>파트구분</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>공정순서</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>공정명</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>기준단가(원)</t>
         </is>
@@ -455,15 +460,20 @@
           <t>VVT 스프로킷</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>120</v>
       </c>
     </row>
@@ -478,15 +488,20 @@
           <t>VVT 스프로킷</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>260</v>
       </c>
     </row>
@@ -501,15 +516,20 @@
           <t>VVT 스프로킷</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>310</v>
       </c>
     </row>
@@ -524,15 +544,20 @@
           <t>VVT 스프로킷</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>335</v>
       </c>
     </row>
@@ -547,15 +572,20 @@
           <t>오일펌프 로터</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>95</v>
       </c>
     </row>
@@ -570,15 +600,20 @@
           <t>오일펌프 로터</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>210</v>
       </c>
     </row>
@@ -593,15 +628,20 @@
           <t>오일펌프 로터</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>250</v>
       </c>
     </row>
@@ -616,15 +656,20 @@
           <t>오일펌프 로터</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>268</v>
       </c>
     </row>
@@ -639,15 +684,20 @@
           <t>캠 로브</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>140</v>
       </c>
     </row>
@@ -662,15 +712,20 @@
           <t>캠 로브</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>300</v>
       </c>
     </row>
@@ -685,15 +740,20 @@
           <t>캠 로브</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>360</v>
       </c>
     </row>
@@ -708,15 +768,20 @@
           <t>캠 로브</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>390</v>
       </c>
     </row>
@@ -731,15 +796,20 @@
           <t>베인</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>80</v>
       </c>
     </row>
@@ -754,15 +824,20 @@
           <t>베인</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>175</v>
       </c>
     </row>
@@ -777,15 +852,20 @@
           <t>베인</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>210</v>
       </c>
     </row>
@@ -800,15 +880,20 @@
           <t>베인</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>4</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>226</v>
       </c>
     </row>
@@ -823,15 +908,20 @@
           <t>부싱</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>60</v>
       </c>
     </row>
@@ -846,15 +936,20 @@
           <t>부싱</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>130</v>
       </c>
     </row>
@@ -869,15 +964,20 @@
           <t>부싱</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>158</v>
       </c>
     </row>
@@ -892,15 +992,20 @@
           <t>부싱</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VMS PART</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>170</v>
       </c>
     </row>
@@ -915,15 +1020,20 @@
           <t>스테이터 코어</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>150</v>
       </c>
     </row>
@@ -938,15 +1048,20 @@
           <t>스테이터 코어</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>320</v>
       </c>
     </row>
@@ -961,15 +1076,20 @@
           <t>스테이터 코어</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>3</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>390</v>
       </c>
     </row>
@@ -984,15 +1104,20 @@
           <t>스테이터 코어</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>4</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>420</v>
       </c>
     </row>
@@ -1007,15 +1132,20 @@
           <t>샤프트</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>110</v>
       </c>
     </row>
@@ -1030,15 +1160,20 @@
           <t>샤프트</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>2</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>240</v>
       </c>
     </row>
@@ -1053,15 +1188,20 @@
           <t>샤프트</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>285</v>
       </c>
     </row>
@@ -1076,15 +1216,20 @@
           <t>샤프트</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>4</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>305</v>
       </c>
     </row>
@@ -1099,15 +1244,20 @@
           <t>커뮤테이터</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>175</v>
       </c>
     </row>
@@ -1122,15 +1272,20 @@
           <t>커뮤테이터</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>2</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>360</v>
       </c>
     </row>
@@ -1145,15 +1300,20 @@
           <t>커뮤테이터</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>3</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>430</v>
       </c>
     </row>
@@ -1168,15 +1328,20 @@
           <t>커뮤테이터</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>4</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>465</v>
       </c>
     </row>
@@ -1191,15 +1356,20 @@
           <t>하우징</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>90</v>
       </c>
     </row>
@@ -1214,15 +1384,20 @@
           <t>하우징</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>2</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>195</v>
       </c>
     </row>
@@ -1237,15 +1412,20 @@
           <t>하우징</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>3</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>235</v>
       </c>
     </row>
@@ -1260,15 +1440,20 @@
           <t>하우징</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>252</v>
       </c>
     </row>
@@ -1283,15 +1468,20 @@
           <t>마그넷 요크</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>1</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>성형</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>130</v>
       </c>
     </row>
@@ -1306,15 +1496,20 @@
           <t>마그넷 요크</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>2</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>소결</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>280</v>
       </c>
     </row>
@@ -1329,15 +1524,20 @@
           <t>마그넷 요크</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>3</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>정형</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>335</v>
       </c>
     </row>
@@ -1352,15 +1552,20 @@
           <t>마그넷 요크</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TM PART</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>선별</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>360</v>
       </c>
     </row>
